--- a/AAII_Financials/Yearly/LCII_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LCII_YR_FIN.xlsx
@@ -1059,13 +1059,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>65200</v>
+        <v>121200</v>
       </c>
       <c r="E15" s="3">
-        <v>68900</v>
+        <v>125700</v>
       </c>
       <c r="F15" s="3">
-        <v>74600</v>
+        <v>131800</v>
       </c>
       <c r="G15" s="3">
         <v>63000</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>345100</v>
+        <v>401200</v>
       </c>
       <c r="E21" s="3">
-        <v>287200</v>
+        <v>343900</v>
       </c>
       <c r="F21" s="3">
-        <v>198100</v>
+        <v>255200</v>
       </c>
       <c r="G21" s="3">
         <v>616000</v>
